--- a/Results/Study 1/Confusion Matrices (train images).xlsx
+++ b/Results/Study 1/Confusion Matrices (train images).xlsx
@@ -610,21 +610,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>527</v>
-      </c>
-      <c r="C2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>118</v>
-      </c>
-      <c r="C3">
-        <v>522</v>
+        <v>537</v>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>125</v>
+      </c>
+      <c r="C3">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -650,21 +650,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>508</v>
-      </c>
-      <c r="C2">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>213</v>
-      </c>
-      <c r="C3">
-        <v>427</v>
+        <v>495</v>
+      </c>
+      <c r="C2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>218</v>
+      </c>
+      <c r="C3">
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 1/Confusion Matrices (train images).xlsx
+++ b/Results/Study 1/Confusion Matrices (train images).xlsx
@@ -410,21 +410,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>369</v>
-      </c>
-      <c r="C2">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>266</v>
-      </c>
-      <c r="C3">
-        <v>374</v>
+        <v>452</v>
+      </c>
+      <c r="C2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>355</v>
+      </c>
+      <c r="C3">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -450,21 +450,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>461</v>
-      </c>
-      <c r="C2">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>154</v>
-      </c>
-      <c r="C3">
-        <v>486</v>
+        <v>464</v>
+      </c>
+      <c r="C2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -530,21 +530,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>380</v>
-      </c>
-      <c r="C2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>196</v>
-      </c>
-      <c r="C3">
-        <v>444</v>
+        <v>585</v>
+      </c>
+      <c r="C2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>207</v>
+      </c>
+      <c r="C3">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -570,21 +570,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>485</v>
-      </c>
-      <c r="C2">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>189</v>
-      </c>
-      <c r="C3">
-        <v>451</v>
+        <v>490</v>
+      </c>
+      <c r="C2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>182</v>
+      </c>
+      <c r="C3">
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -610,222 +610,222 @@
         <v>2</v>
       </c>
       <c r="B2">
+        <v>540</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>105</v>
+      </c>
+      <c r="C3">
+        <v>535</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>528</v>
+      </c>
+      <c r="C2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>194</v>
+      </c>
+      <c r="C3">
+        <v>446</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>382</v>
+      </c>
+      <c r="C2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>109</v>
+      </c>
+      <c r="C3">
+        <v>531</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>445</v>
+      </c>
+      <c r="C2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>137</v>
+      </c>
+      <c r="C3">
+        <v>503</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>479</v>
+      </c>
+      <c r="C2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>105</v>
+      </c>
+      <c r="C3">
+        <v>535</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>471</v>
+      </c>
+      <c r="C2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>103</v>
+      </c>
+      <c r="C3">
         <v>537</v>
       </c>
-      <c r="C2">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>125</v>
-      </c>
-      <c r="C3">
-        <v>515</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>495</v>
-      </c>
-      <c r="C2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>218</v>
-      </c>
-      <c r="C3">
-        <v>422</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>417</v>
-      </c>
-      <c r="C2">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>124</v>
-      </c>
-      <c r="C3">
-        <v>516</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>541</v>
-      </c>
-      <c r="C2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>351</v>
-      </c>
-      <c r="C3">
-        <v>289</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>512</v>
-      </c>
-      <c r="C2">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>144</v>
-      </c>
-      <c r="C3">
-        <v>496</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>330</v>
-      </c>
-      <c r="C2">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>161</v>
-      </c>
-      <c r="C3">
-        <v>479</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -850,21 +850,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>192</v>
-      </c>
-      <c r="C2">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>192</v>
-      </c>
-      <c r="C3">
-        <v>448</v>
+        <v>256</v>
+      </c>
+      <c r="C2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>256</v>
+      </c>
+      <c r="C3">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
